--- a/docs/deliverables/06_リリース/リリースノート_v0.9.0-rc1.xlsx
+++ b/docs/deliverables/06_リリース/リリースノート_v0.9.0-rc1.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="文書管理" sheetId="1" r:id="R92e5aa4174ab42e7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v0.9.0-rc1" sheetId="2" r:id="Reee24f8b1aba47f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="テスト状況" sheetId="3" r:id="R3290c0e6db904682"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主な機能" sheetId="4" r:id="Rbf9bb2a3357d4b67"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セキュリティ" sheetId="5" r:id="Rf5f3ec2bc6724543"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="既知の制約" sheetId="6" r:id="R7e697ace5186459a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="正式リリースへの条件" sheetId="7" r:id="Rfcb7f8da58884b3f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="文書管理" sheetId="1" r:id="R1eff59d4c91d452d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v0.9.0-rc1" sheetId="2" r:id="R3813a7c50eae403d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="テスト状況" sheetId="3" r:id="R2dc2c77a7c0b4ec7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主な機能" sheetId="4" r:id="R5c6d8ef2efaa454d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セキュリティ" sheetId="5" r:id="Rd03d781372d740a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="既知の制約" sheetId="6" r:id="R7ce036282dc44480"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="正式リリースへの条件" sheetId="7" r:id="R08827c97ef6845b0"/>
   </x:sheets>
 </x:workbook>
 </file>
